--- a/excel/container.xlsx
+++ b/excel/container.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12360"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -148,10 +148,10 @@
     <t>itemNumWeight</t>
   </si>
   <si>
-    <t>string</t>
+    <t>int</t>
   </si>
   <si>
-    <t>int</t>
+    <t>string</t>
   </si>
   <si>
     <t>物资盒</t>
@@ -1221,16 +1221,16 @@
         <v>10</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>10</v>
-      </c>
       <c r="D3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" spans="1:7">
